--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39D.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>49006</t>
   </si>
@@ -121,49 +121,34 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/4to_Trimestre/SEXTA%20ACTA.pdf</t>
-  </si>
-  <si>
-    <t>Unidad de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
+    <t>199EC8672FCEF290BAD468DFE3026497</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Transparencia/20230704133036.pdf</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>12/04/2023</t>
+  </si>
+  <si>
+    <t>23/01/2023</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/4to_Trimestre/acta%20transparencia%205.pdf</t>
-  </si>
-  <si>
-    <t>E6764F407345198E9F8F425874C70101</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>CD27DA3C2D519650C60499A2BFB06CC5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
 </sst>
 </file>
@@ -556,17 +541,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="145.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="100.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
@@ -733,78 +717,40 @@
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
